--- a/tests/estabilidad de agregados1.xlsx
+++ b/tests/estabilidad de agregados1.xlsx
@@ -20,9 +20,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
-  <si>
-    <t xml:space="preserve">DATOS DE Retención Humedad</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="48">
+  <si>
+    <t xml:space="preserve">DATOS DE estabilidad de agregados</t>
   </si>
   <si>
     <t xml:space="preserve">IDLAB</t>
@@ -31,16 +31,16 @@
     <t xml:space="preserve">Rep</t>
   </si>
   <si>
-    <t xml:space="preserve">Peso Total suelo seco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peso conjunto tamices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Temperatura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Humedad Ambiental</t>
+    <t xml:space="preserve">Peso Total suelo seco (g)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peso conjunto tamices (g)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temperatura (°C)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Humedad Ambiental (%)</t>
   </si>
   <si>
     <t xml:space="preserve">Fecha inicio</t>
@@ -49,13 +49,121 @@
     <t xml:space="preserve">12.45</t>
   </si>
   <si>
+    <t xml:space="preserve">225.80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3</t>
+  </si>
+  <si>
     <t xml:space="preserve">12.38</t>
   </si>
   <si>
+    <t xml:space="preserve">21.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4</t>
+  </si>
+  <si>
     <t xml:space="preserve">13.02</t>
   </si>
   <si>
+    <t xml:space="preserve">231.40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1</t>
+  </si>
+  <si>
     <t xml:space="preserve">12.97</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">228.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">233.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.98</t>
+  </si>
+  <si>
+    <t xml:space="preserve">224.70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">232.30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.76</t>
+  </si>
+  <si>
+    <t xml:space="preserve">229.50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">231.60</t>
   </si>
 </sst>
 </file>
@@ -66,7 +174,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -91,6 +199,13 @@
     <font>
       <b val="true"/>
       <sz val="14"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
@@ -145,7 +260,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -162,8 +277,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -190,37 +313,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -293,7 +416,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.2"/>
@@ -348,128 +471,427 @@
       <c r="G2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="A3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="1" t="n">
-        <v>226</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>215</v>
-      </c>
-      <c r="F3" s="1" t="n">
-        <v>209</v>
-      </c>
-      <c r="G3" s="5" t="n">
+      <c r="D3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="G3" s="7" t="n">
         <v>46068</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="A4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="1" t="n">
-        <v>229</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>218</v>
-      </c>
-      <c r="F4" s="1" t="n">
-        <v>212</v>
-      </c>
-      <c r="G4" s="5" t="n">
+      <c r="E4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="G4" s="7" t="n">
         <v>46068</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="A5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>46068</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>46068</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>46068</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>46068</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>46068</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>62</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>46068</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>46068</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>46069</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>46069</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>63</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>46069</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="1" t="n">
-        <v>241</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>233</v>
-      </c>
-      <c r="F5" s="1" t="n">
-        <v>227</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>46068</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>238</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>231</v>
-      </c>
-      <c r="F6" s="1" t="n">
-        <v>225</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>46068</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>229</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>218</v>
-      </c>
-      <c r="F7" s="1" t="n">
-        <v>212</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>46068</v>
+      <c r="F15" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>46069</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>46069</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>46069</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>46070</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>46070</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>46070</v>
       </c>
     </row>
   </sheetData>

--- a/tests/estabilidad de agregados1.xlsx
+++ b/tests/estabilidad de agregados1.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t xml:space="preserve">DATOS DE Retención Humedad</t>
   </si>
@@ -31,31 +31,34 @@
     <t xml:space="preserve">Rep</t>
   </si>
   <si>
-    <t xml:space="preserve">Peso Total suelo seco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peso conjunto tamices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Temperatura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Humedad Ambiental</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fecha inicio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.97</t>
+    <t xml:space="preserve">T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRI2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRI1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRI05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRI025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRI0</t>
   </si>
 </sst>
 </file>
@@ -166,7 +169,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -190,37 +193,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -299,10 +302,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.2"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="26.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="33.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="29.81"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="26.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="29.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="4" style="1" width="14.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="11.38"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="15" min="9" style="1" width="11.53"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="17" style="1" width="11.53"/>
   </cols>
@@ -348,11 +349,21 @@
       <c r="G2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
+      <c r="H2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="M2" s="4"/>
       <c r="N2" s="4"/>
       <c r="O2" s="4"/>
@@ -364,21 +375,7 @@
       <c r="B3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>226</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>215</v>
-      </c>
-      <c r="F3" s="1" t="n">
-        <v>209</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>46068</v>
-      </c>
+      <c r="G3" s="5"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
@@ -387,21 +384,7 @@
       <c r="B4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>229</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>218</v>
-      </c>
-      <c r="F4" s="1" t="n">
-        <v>212</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>46068</v>
-      </c>
+      <c r="G4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
@@ -410,21 +393,7 @@
       <c r="B5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>241</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>233</v>
-      </c>
-      <c r="F5" s="1" t="n">
-        <v>227</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>46068</v>
-      </c>
+      <c r="G5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
@@ -433,21 +402,7 @@
       <c r="B6" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>238</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>231</v>
-      </c>
-      <c r="F6" s="1" t="n">
-        <v>225</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>46068</v>
-      </c>
+      <c r="G6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
@@ -456,21 +411,7 @@
       <c r="B7" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>229</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>218</v>
-      </c>
-      <c r="F7" s="1" t="n">
-        <v>212</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>46068</v>
-      </c>
+      <c r="G7" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/tests/estabilidad de agregados1.xlsx
+++ b/tests/estabilidad de agregados1.xlsx
@@ -20,15 +20,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="16">
   <si>
-    <t xml:space="preserve">DATOS DE Retención Humedad</t>
+    <t xml:space="preserve">DATOS DE Estabilidad de Agregados</t>
   </si>
   <si>
     <t xml:space="preserve">IDLAB</t>
   </si>
   <si>
     <t xml:space="preserve">Rep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PESO SECO</t>
   </si>
   <si>
     <t xml:space="preserve">T2</t>
@@ -60,14 +63,19 @@
   <si>
     <t xml:space="preserve">PRI0</t>
   </si>
+  <si>
+    <t xml:space="preserve">0.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.25</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -148,7 +156,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -167,10 +175,6 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -296,16 +300,17 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.2"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="26.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="4" style="1" width="14.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="11.38"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="15" min="9" style="1" width="11.53"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="17" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="5" style="1" width="14.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="11.38"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16" min="10" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="18" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -318,7 +323,7 @@
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
-      <c r="H1" s="3"/>
+      <c r="H1" s="2"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
@@ -326,6 +331,7 @@
       <c r="M1" s="3"/>
       <c r="N1" s="3"/>
       <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
@@ -364,58 +370,1205 @@
       <c r="L2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="4"/>
+      <c r="M2" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="N2" s="4"/>
       <c r="O2" s="4"/>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P2" s="4"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
-        <v>1</v>
+        <v>1001</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G3" s="5"/>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C3" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K3" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="L3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="1" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
-        <v>1</v>
+        <v>1002</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="G4" s="5"/>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>101</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K4" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="L4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
-        <v>2</v>
+        <v>1003</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="5"/>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C5" s="1" t="n">
+        <v>102</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="L5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
-        <v>2</v>
+        <v>1004</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" s="5"/>
+        <v>1</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>103</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="L6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
-        <v>3</v>
+        <v>1005</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="5"/>
+      <c r="C7" s="1" t="n">
+        <v>104</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
+        <v>1005</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="n">
+        <v>1006</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>106</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="L9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="n">
+        <v>1007</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>107</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I10" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="L10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="1" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="n">
+        <v>1008</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K11" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="L11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="1" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="n">
+        <v>1009</v>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>109</v>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I12" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K12" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="L12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="1" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="n">
+        <v>1010</v>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>110</v>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K13" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="L13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="1" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="n">
+        <v>1011</v>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>111</v>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K14" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="L14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="1" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="n">
+        <v>1012</v>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>112</v>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I15" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K15" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="L15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="1" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="n">
+        <v>1013</v>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>113</v>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I16" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K16" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="L16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="1" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="n">
+        <v>1014</v>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>114</v>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I17" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K17" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="L17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="1" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="n">
+        <v>1015</v>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>115</v>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I18" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K18" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="L18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="1" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="n">
+        <v>1016</v>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>116</v>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="F19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I19" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K19" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="L19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="1" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="n">
+        <v>1017</v>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>117</v>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="F20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I20" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="L20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="1" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="n">
+        <v>1018</v>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="1" t="n">
+        <v>118</v>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="F21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I21" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K21" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="L21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="1" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="n">
+        <v>1019</v>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="1" t="n">
+        <v>119</v>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="F22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I22" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K22" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="L22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="1" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="n">
+        <v>1020</v>
+      </c>
+      <c r="B23" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="F23" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I23" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K23" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="L23" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="1" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="n">
+        <v>1021</v>
+      </c>
+      <c r="B24" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="1" t="n">
+        <v>121</v>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F24" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I24" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K24" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="L24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="1" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="n">
+        <v>1022</v>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="1" t="n">
+        <v>122</v>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="F25" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I25" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K25" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="L25" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="1" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="n">
+        <v>1023</v>
+      </c>
+      <c r="B26" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="1" t="n">
+        <v>123</v>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="F26" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I26" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K26" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="L26" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="1" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="n">
+        <v>1024</v>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="1" t="n">
+        <v>124</v>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="F27" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I27" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K27" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="L27" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="1" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="n">
+        <v>1025</v>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="1" t="n">
+        <v>125</v>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="F28" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I28" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="L28" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="1" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="n">
+        <v>1026</v>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="1" t="n">
+        <v>126</v>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="F29" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I29" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K29" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="L29" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="1" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="n">
+        <v>1027</v>
+      </c>
+      <c r="B30" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="1" t="n">
+        <v>127</v>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="F30" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I30" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K30" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="L30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="1" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="n">
+        <v>1028</v>
+      </c>
+      <c r="B31" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" s="1" t="n">
+        <v>128</v>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="F31" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I31" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K31" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="L31" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="1" t="n">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
